--- a/inputs/data_symbols_TD/18_LTAN06_800km_1213COLD_PY_STTLCT_PROP_HEAT_PY_0p5.xlsx
+++ b/inputs/data_symbols_TD/18_LTAN06_800km_1213COLD_PY_STTLCT_PROP_HEAT_PY_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C19B8DE0-75A8-42F5-9177-72A9D7062A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13981295-FC79-41E3-871D-0DC34D78DB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B8965851-DA03-4DB3-AD66-16C40D375E11}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{E02F69D0-76BD-405C-8516-711AB008CECB}"/>
   </bookViews>
   <sheets>
     <sheet name="18_LTAN06_800km_1213COLD_PY_STT" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C61969-548F-423C-8E88-DA97A7FDE8AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CA540E3-BE65-406D-9C57-3E99A3A3FB56}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
